--- a/tests/testthat/_output_excel_snaps/dataframe_to_sheet.xlsx
+++ b/tests/testthat/_output_excel_snaps/dataframe_to_sheet.xlsx
@@ -134,16 +134,16 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -167,16 +167,16 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
